--- a/performance_data_graphite/train/metrics.xlsx
+++ b/performance_data_graphite/train/metrics.xlsx
@@ -468,7 +468,7 @@
         <v>2.785058907342028</v>
       </c>
       <c r="E2" t="n">
-        <v>4.623990253207506</v>
+        <v>8.286382797790747</v>
       </c>
     </row>
     <row r="3">
@@ -489,7 +489,7 @@
         <v>1.977815894646275</v>
       </c>
       <c r="E3" t="n">
-        <v>2.616296697214296</v>
+        <v>6.276870428678328</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         <v>1.368557701395978</v>
       </c>
       <c r="E4" t="n">
-        <v>1.132596768888091</v>
+        <v>3.824731809104187</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +531,7 @@
         <v>1.117847302570005</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6983918983167832</v>
+        <v>2.720885832094238</v>
       </c>
     </row>
     <row r="6">
@@ -552,7 +552,7 @@
         <v>0.8523313504263444</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3531194125255145</v>
+        <v>1.592965607921798</v>
       </c>
     </row>
     <row r="7">
@@ -573,7 +573,7 @@
         <v>0.5766694847886016</v>
       </c>
       <c r="E7" t="n">
-        <v>0.124973727147891</v>
+        <v>0.6261769256677279</v>
       </c>
     </row>
     <row r="8">
@@ -594,7 +594,7 @@
         <v>0.3000143927945563</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0363461990295041</v>
+        <v>0.1132736341547892</v>
       </c>
     </row>
     <row r="9">
@@ -615,7 +615,7 @@
         <v>0.3198165106180806</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2103175274952571</v>
+        <v>0.2920602157916234</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         <v>1.554554453209885</v>
       </c>
       <c r="E10" t="n">
-        <v>2.431790974792472</v>
+        <v>2.581399218231885</v>
       </c>
     </row>
     <row r="11">
@@ -657,7 +657,7 @@
         <v>9.998765111665252</v>
       </c>
       <c r="E11" t="n">
-        <v>3.029179690698491</v>
+        <v>3.003024363939751</v>
       </c>
     </row>
     <row r="12">
@@ -678,7 +678,7 @@
         <v>15.20485508929449</v>
       </c>
       <c r="E12" t="n">
-        <v>2.918123068161838</v>
+        <v>2.714605402868227</v>
       </c>
     </row>
     <row r="13">
@@ -699,7 +699,7 @@
         <v>15.91267928314373</v>
       </c>
       <c r="E13" t="n">
-        <v>2.439703877099446</v>
+        <v>5.809167146881697</v>
       </c>
     </row>
     <row r="14">
@@ -720,7 +720,7 @@
         <v>15.4089752751182</v>
       </c>
       <c r="E14" t="n">
-        <v>2.189944419698</v>
+        <v>9.677740285821697</v>
       </c>
     </row>
     <row r="15">
@@ -741,7 +741,7 @@
         <v>12.81885674020423</v>
       </c>
       <c r="E15" t="n">
-        <v>2.760096666434418</v>
+        <v>5.102317391576658</v>
       </c>
     </row>
     <row r="16">
@@ -762,7 +762,7 @@
         <v>0.9312699179625071</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4897308843805571</v>
+        <v>0.7967048080595902</v>
       </c>
     </row>
     <row r="17">
@@ -783,7 +783,7 @@
         <v>8.0821724247283</v>
       </c>
       <c r="E17" t="n">
-        <v>4.507068533848618</v>
+        <v>5.6409585659461</v>
       </c>
     </row>
     <row r="18">
@@ -804,7 +804,7 @@
         <v>0.9152260972278605</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4137568882251523</v>
+        <v>0.6251368611633753</v>
       </c>
     </row>
     <row r="19">
@@ -825,7 +825,7 @@
         <v>6.685815413274751</v>
       </c>
       <c r="E19" t="n">
-        <v>3.315921674862683</v>
+        <v>5.469944339194605</v>
       </c>
     </row>
     <row r="20">
@@ -846,7 +846,7 @@
         <v>0.83831168071832</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3573804176907943</v>
+        <v>0.4454329500334456</v>
       </c>
     </row>
     <row r="21">
@@ -867,7 +867,7 @@
         <v>5.898471842534359</v>
       </c>
       <c r="E21" t="n">
-        <v>2.766936547575129</v>
+        <v>3.548816306255338</v>
       </c>
     </row>
     <row r="22">
@@ -888,7 +888,7 @@
         <v>3.721854702480273</v>
       </c>
       <c r="E22" t="n">
-        <v>2.943560092183104</v>
+        <v>3.060965788028126</v>
       </c>
     </row>
     <row r="23">
@@ -909,7 +909,7 @@
         <v>4.821207661227971</v>
       </c>
       <c r="E23" t="n">
-        <v>4.215591544955481</v>
+        <v>4.641596334345145</v>
       </c>
     </row>
   </sheetData>
